--- a/artfynd/A 5737-2026 artfynd.xlsx
+++ b/artfynd/A 5737-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>338009</v>
+        <v>97362280</v>
       </c>
       <c r="B2" t="n">
-        <v>89391</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mjövattenberget, SO delen, Ång</t>
+          <t>Mjövattenberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560288.3387335661</v>
+        <v>560373</v>
       </c>
       <c r="R2" t="n">
-        <v>7085994.229492978</v>
+        <v>7085968</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1996-10-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1996-10-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Källa: Skogsstyrelsens nyckelbiotopsregister</t>
+          <t>2021-06-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,41 +756,30 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog med inslag av lövträd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Dan Olofsson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Griph</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97362279</v>
+        <v>97362272</v>
       </c>
       <c r="B3" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,12 +796,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560372.3748080883</v>
+        <v>560298</v>
       </c>
       <c r="R3" t="n">
-        <v>7086005.540364077</v>
+        <v>7086202</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,19 +844,9 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-06-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97362274</v>
+        <v>97362279</v>
       </c>
       <c r="B4" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220093</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560302.9327187295</v>
+        <v>560372</v>
       </c>
       <c r="R4" t="n">
-        <v>7086175.569666804</v>
+        <v>7086005</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,19 +945,9 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-06-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97362300</v>
+        <v>97362303</v>
       </c>
       <c r="B5" t="n">
-        <v>94440</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1841</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1074,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560147.8408164377</v>
+        <v>559916</v>
       </c>
       <c r="R5" t="n">
-        <v>7086120.605163704</v>
+        <v>7086181</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,19 +1046,9 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-06-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97362318</v>
+        <v>97362304</v>
       </c>
       <c r="B6" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559927.3114799857</v>
+        <v>559889</v>
       </c>
       <c r="R6" t="n">
-        <v>7086257.783179942</v>
+        <v>7086220</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,19 +1147,9 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-06-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97362275</v>
+        <v>338009</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,37 +1191,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mjövattenberget, Ång</t>
+          <t>Mjövattenberget, SO delen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560312.099078242</v>
+        <v>560288</v>
       </c>
       <c r="R7" t="n">
-        <v>7086157.684793779</v>
+        <v>7085994</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,22 +1245,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1996-10-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-06-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1996-10-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Källa: Skogsstyrelsens nyckelbiotopsregister</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,35 +1266,36 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrskog med inslag av lövträd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Dan Olofsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Anders Griph</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97362324</v>
+        <v>97362278</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560019.9911032501</v>
+        <v>560368</v>
       </c>
       <c r="R8" t="n">
-        <v>7086278.059433335</v>
+        <v>7085999</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,21 +1360,11 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-06-18</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1478,11 +1373,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1503,37 +1393,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97362322</v>
+        <v>97362282</v>
       </c>
       <c r="B9" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1543,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560008.1264062026</v>
+        <v>560419</v>
       </c>
       <c r="R9" t="n">
-        <v>7086252.723186946</v>
+        <v>7085912</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,21 +1461,11 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-06-18</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1599,11 +1474,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1624,15 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97362303</v>
+        <v>97362320</v>
       </c>
       <c r="B10" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,21 +1505,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1664,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559915.9992251883</v>
+        <v>559964</v>
       </c>
       <c r="R10" t="n">
-        <v>7086180.477078075</v>
+        <v>7086261</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1697,19 +1562,9 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-06-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,15 +1595,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97362280</v>
+        <v>97362323</v>
       </c>
       <c r="B11" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,21 +1606,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1780,10 +1630,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560372.6639416585</v>
+        <v>560022</v>
       </c>
       <c r="R11" t="n">
-        <v>7085967.658848628</v>
+        <v>7086262</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1813,21 +1663,11 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-06-18</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1836,6 +1676,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1856,15 +1701,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97362278</v>
+        <v>97362273</v>
       </c>
       <c r="B12" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,21 +1712,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1896,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560368.0840931529</v>
+        <v>560292</v>
       </c>
       <c r="R12" t="n">
-        <v>7085999.290018554</v>
+        <v>7086179</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1929,19 +1769,9 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-06-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1972,37 +1802,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97362276</v>
+        <v>97362277</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2012,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560311.429233141</v>
+        <v>560368</v>
       </c>
       <c r="R13" t="n">
-        <v>7086146.658793808</v>
+        <v>7086004</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2045,19 +1870,9 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-06-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2088,15 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97362272</v>
+        <v>97362305</v>
       </c>
       <c r="B14" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,21 +1914,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2128,10 +1938,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560297.5822030033</v>
+        <v>559884</v>
       </c>
       <c r="R14" t="n">
-        <v>7086201.457247738</v>
+        <v>7086216</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2161,21 +1971,11 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-06-18</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2184,6 +1984,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2204,15 +2009,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97362323</v>
+        <v>97362300</v>
       </c>
       <c r="B15" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,21 +2020,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1841</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2244,10 +2044,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560022.0670642171</v>
+        <v>560147</v>
       </c>
       <c r="R15" t="n">
-        <v>7086261.800512781</v>
+        <v>7086121</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2277,21 +2077,11 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-06-18</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2300,11 +2090,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2328,12 +2113,7 @@
         <v>97362281</v>
       </c>
       <c r="B16" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,10 +2145,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560391.2365057324</v>
+        <v>560391</v>
       </c>
       <c r="R16" t="n">
-        <v>7085919.556029059</v>
+        <v>7085920</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2398,19 +2178,9 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-06-18</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2446,37 +2216,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97362299</v>
+        <v>97362317</v>
       </c>
       <c r="B17" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2486,10 +2251,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560225.6544449978</v>
+        <v>559824</v>
       </c>
       <c r="R17" t="n">
-        <v>7085973.639340437</v>
+        <v>7086316</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2519,21 +2284,11 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-06-18</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2545,7 +2300,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2570,12 +2325,7 @@
         <v>97362316</v>
       </c>
       <c r="B18" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559813.5647060052</v>
+        <v>559813</v>
       </c>
       <c r="R18" t="n">
-        <v>7086324.326700419</v>
+        <v>7086324</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2640,19 +2390,9 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2021-06-18</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2683,37 +2423,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97362273</v>
+        <v>97362318</v>
       </c>
       <c r="B19" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2723,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560291.8500745487</v>
+        <v>559927</v>
       </c>
       <c r="R19" t="n">
-        <v>7086178.439915157</v>
+        <v>7086258</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2756,19 +2491,9 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-06-18</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2799,37 +2524,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>97362304</v>
+        <v>97362326</v>
       </c>
       <c r="B20" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6457</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2839,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559889.6756963787</v>
+        <v>560016</v>
       </c>
       <c r="R20" t="n">
-        <v>7086219.179353777</v>
+        <v>7086333</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2872,21 +2592,11 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-06-18</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2895,6 +2605,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2915,37 +2630,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>97362317</v>
+        <v>97362275</v>
       </c>
       <c r="B21" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2955,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559824.3232236143</v>
+        <v>560313</v>
       </c>
       <c r="R21" t="n">
-        <v>7086315.281774439</v>
+        <v>7086157</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2988,21 +2698,11 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-06-18</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3011,11 +2711,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3036,15 +2731,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>97362320</v>
+        <v>97362299</v>
       </c>
       <c r="B22" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3052,21 +2742,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3076,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559964.3150305826</v>
+        <v>560226</v>
       </c>
       <c r="R22" t="n">
-        <v>7086260.253573136</v>
+        <v>7085974</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3109,21 +2799,11 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-06-18</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3132,6 +2812,11 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3155,12 +2840,7 @@
         <v>97362302</v>
       </c>
       <c r="B23" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3192,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>559971.1999131372</v>
+        <v>559971</v>
       </c>
       <c r="R23" t="n">
-        <v>7086177.12854271</v>
+        <v>7086177</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3225,19 +2905,9 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2021-06-18</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3273,37 +2943,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>97362301</v>
+        <v>97362306</v>
       </c>
       <c r="B24" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3313,10 +2978,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560031.7237228426</v>
+        <v>559869</v>
       </c>
       <c r="R24" t="n">
-        <v>7086149.213836579</v>
+        <v>7086206</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3346,19 +3011,9 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2021-06-18</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3397,12 +3052,7 @@
         <v>97362319</v>
       </c>
       <c r="B25" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3434,10 +3084,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>559945.2964754619</v>
+        <v>559945</v>
       </c>
       <c r="R25" t="n">
-        <v>7086262.972987607</v>
+        <v>7086263</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3467,19 +3117,9 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2021-06-18</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3515,37 +3155,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>97362277</v>
+        <v>97362324</v>
       </c>
       <c r="B26" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3555,10 +3190,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560368.4231832606</v>
+        <v>560020</v>
       </c>
       <c r="R26" t="n">
-        <v>7086004.583099373</v>
+        <v>7086278</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3588,21 +3223,11 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2021-06-18</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3611,6 +3236,11 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3631,37 +3261,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>97362282</v>
+        <v>97362301</v>
       </c>
       <c r="B27" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3671,10 +3296,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560419.1704122913</v>
+        <v>560031</v>
       </c>
       <c r="R27" t="n">
-        <v>7085912.16475976</v>
+        <v>7086149</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3704,21 +3329,11 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2021-06-18</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3727,6 +3342,11 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3747,37 +3367,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>97362305</v>
+        <v>97362274</v>
       </c>
       <c r="B28" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>220093</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3787,10 +3402,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>559884.8760425517</v>
+        <v>560303</v>
       </c>
       <c r="R28" t="n">
-        <v>7086216.444491064</v>
+        <v>7086176</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3820,21 +3435,11 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2021-06-18</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3843,11 +3448,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3868,37 +3468,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>97362306</v>
+        <v>97362276</v>
       </c>
       <c r="B29" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3908,10 +3503,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>559868.7554173231</v>
+        <v>560311</v>
       </c>
       <c r="R29" t="n">
-        <v>7086206.004451331</v>
+        <v>7086146</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3941,21 +3536,11 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2021-06-18</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3964,11 +3549,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3982,6 +3562,112 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>97362322</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mjövattenberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>560008</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7086253</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bodum</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2021-06-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>

--- a/artfynd/A 5737-2026 artfynd.xlsx
+++ b/artfynd/A 5737-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362280</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362272</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362279</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362303</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362304</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/338009</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,6 +1425,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362278</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1491,6 +1531,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362282</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1592,6 +1637,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362320</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1698,6 +1748,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362323</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,6 +1854,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362273</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1900,6 +1960,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362277</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2006,6 +2071,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362305</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2107,6 +2177,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362300</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2213,6 +2288,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362281</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2319,6 +2399,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362317</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2420,6 +2505,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362316</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2521,6 +2611,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362318</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2627,6 +2722,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362326</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2728,6 +2828,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362275</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2834,6 +2939,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362299</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2940,6 +3050,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362302</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3046,6 +3161,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362306</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3152,6 +3272,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362319</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3258,6 +3383,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362324</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3364,6 +3494,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362301</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3465,6 +3600,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362274</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3566,6 +3706,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362276</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3672,8 +3817,44 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362322</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>